--- a/mlef_pipeline/results/OS_6/HIGH_PDL1/RWD/results.xlsx
+++ b/mlef_pipeline/results/OS_6/HIGH_PDL1/RWD/results.xlsx
@@ -473,17 +473,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.52 ± 0.06</t>
+          <t>0.55 ± 0.07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.56 ± 0.19</t>
+          <t>0.65 ± 0.18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.65 ± 0.26</t>
+          <t>0.58 ± 0.28</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,22 +498,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.70 ± 0.16</t>
+          <t>0.65 ± 0.17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.67 ± 0.15</t>
+          <t>0.76 ± 0.15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F4" t="n">
